--- a/TESTING_FILES/mega_data.xlsx
+++ b/TESTING_FILES/mega_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Amey Gawade\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Amey Gawade\Desktop\MCA_ADITYA\PROJECTS\data-cleaner-app\TESTING_FILES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD421E84-095E-4370-BF20-1AC1B122A1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43233E67-CF24-4A47-B682-518BBD5596C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E294A85-E37C-44A6-8FB7-4D7EA5F08384}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="182">
   <si>
     <t>Name</t>
   </si>
@@ -550,6 +550,36 @@
   </si>
   <si>
     <t>Ad Optimizer</t>
+  </si>
+  <si>
+    <t>hr</t>
+  </si>
+  <si>
+    <t>It</t>
+  </si>
+  <si>
+    <t>fiNanCE</t>
+  </si>
+  <si>
+    <t>Emily CLArke</t>
+  </si>
+  <si>
+    <t>EmMa</t>
+  </si>
+  <si>
+    <t>KolkaTA</t>
+  </si>
+  <si>
+    <t>DelHI</t>
+  </si>
+  <si>
+    <t>MumbAI</t>
+  </si>
+  <si>
+    <t>DeLHi</t>
+  </si>
+  <si>
+    <t>AhmedaBAD</t>
   </si>
 </sst>
 </file>
@@ -1016,7 +1046,7 @@
         <v>17</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>179</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>19</v>
@@ -1054,7 +1084,7 @@
         <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>172</v>
       </c>
       <c r="C3" s="1">
         <v>45000</v>
@@ -1101,7 +1131,7 @@
         <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="C4" s="1">
         <v>60000</v>
@@ -1110,7 +1140,7 @@
         <v>33</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>34</v>
+        <v>178</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>19</v>
@@ -1148,7 +1178,7 @@
         <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>173</v>
       </c>
       <c r="C5" s="1">
         <v>55000</v>
@@ -1192,7 +1222,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>175</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>44</v>
@@ -1298,7 +1328,7 @@
         <v>54</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>55</v>
+        <v>177</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>19</v>
@@ -1380,7 +1410,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>59</v>
+        <v>176</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>26</v>
@@ -1439,7 +1469,7 @@
         <v>63</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>34</v>
+        <v>180</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>19</v>
@@ -1580,7 +1610,7 @@
         <v>67</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>19</v>
